--- a/MR_metaanalysis/gMR_dat.xlsx
+++ b/MR_metaanalysis/gMR_dat.xlsx
@@ -6,19 +6,19 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="ebi-a-GCST006979" r:id="rId3" sheetId="1"/>
+    <sheet name="eBMD" r:id="rId3" sheetId="1"/>
     <sheet name="HF" r:id="rId4" sheetId="2"/>
-    <sheet name="ebi-a-GCST005194" r:id="rId5" sheetId="3"/>
-    <sheet name="ebi-a-GCST011365" r:id="rId6" sheetId="4"/>
+    <sheet name="CAD" r:id="rId5" sheetId="3"/>
+    <sheet name="MI" r:id="rId6" sheetId="4"/>
     <sheet name="IS" r:id="rId7" sheetId="5"/>
-    <sheet name="ukb-b-14057" r:id="rId8" sheetId="6"/>
-    <sheet name="ebi-a-GCST006867" r:id="rId9" sheetId="7"/>
+    <sheet name="Hypertension" r:id="rId8" sheetId="6"/>
+    <sheet name="T2DM" r:id="rId9" sheetId="7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="91">
   <si>
     <t>SNP</t>
   </si>
@@ -62,7 +62,7 @@
     <t>chr</t>
   </si>
   <si>
-    <t>pos.x</t>
+    <t>pos</t>
   </si>
   <si>
     <t>se.outcome</t>
@@ -128,9 +128,6 @@
     <t>exposure</t>
   </si>
   <si>
-    <t>pos.y</t>
-  </si>
-  <si>
     <t>action</t>
   </si>
   <si>
@@ -194,7 +191,7 @@
     <t>17</t>
   </si>
   <si>
-    <t>41773814</t>
+    <t>41774270</t>
   </si>
   <si>
     <t>41777862</t>
@@ -227,7 +224,7 @@
     <t>igd</t>
   </si>
   <si>
-    <t>rs1107748</t>
+    <t>rs1107747</t>
   </si>
   <si>
     <t>Sclerostin</t>
@@ -239,9 +236,6 @@
     <t>base_pair_location</t>
   </si>
   <si>
-    <t>pos</t>
-  </si>
-  <si>
     <t>Hip fracture</t>
   </si>
   <si>
@@ -290,9 +284,6 @@
     <t>ebi-a-GCST006867</t>
   </si>
   <si>
-    <t>41774270</t>
-  </si>
-  <si>
     <t>Type 2 diabetes || id:ebi-a-GCST006867</t>
   </si>
   <si>
@@ -300,9 +291,6 @@
   </si>
   <si>
     <t xml:space="preserve">Type 2 diabetes ||  || </t>
-  </si>
-  <si>
-    <t>rs1107747</t>
   </si>
 </sst>
 </file>
@@ -466,103 +454,100 @@
       <c r="AM1" t="s">
         <v>37</v>
       </c>
-      <c r="AN1" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0346809</v>
+        <v>-0.0349833</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.608329</v>
+        <v>0.609298</v>
       </c>
       <c r="K2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N2" t="s">
         <v>55</v>
       </c>
-      <c r="L2" t="s">
-        <v>55</v>
-      </c>
-      <c r="M2" t="s">
-        <v>55</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>56</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>57</v>
       </c>
-      <c r="P2" t="s">
-        <v>58</v>
-      </c>
       <c r="Q2" t="n">
-        <v>0.00189411</v>
+        <v>0.00190023</v>
       </c>
       <c r="R2" t="n">
         <v>426824.0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.19989E-57</v>
+        <v>6.4003E-58</v>
       </c>
       <c r="T2" t="s">
+        <v>63</v>
+      </c>
+      <c r="U2" t="s">
         <v>64</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>65</v>
       </c>
-      <c r="V2" t="s">
-        <v>66</v>
-      </c>
       <c r="W2" t="s">
+        <v>66</v>
+      </c>
+      <c r="X2" t="s">
         <v>67</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA2" t="s">
         <v>68</v>
       </c>
-      <c r="Y2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>69</v>
-      </c>
       <c r="AB2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AC2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AE2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AF2" t="n">
         <v>1.0</v>
@@ -577,39 +562,36 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="AJ2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AK2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.1773814E7</v>
-      </c>
-      <c r="AM2" t="n">
         <v>2.0</v>
       </c>
-      <c r="AN2" t="s">
-        <v>67</v>
+      <c r="AM2" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
@@ -624,22 +606,22 @@
         <v>0.358972</v>
       </c>
       <c r="K3" t="s">
+        <v>54</v>
+      </c>
+      <c r="L3" t="s">
+        <v>54</v>
+      </c>
+      <c r="M3" t="s">
+        <v>54</v>
+      </c>
+      <c r="N3" t="s">
         <v>55</v>
       </c>
-      <c r="L3" t="s">
-        <v>55</v>
-      </c>
-      <c r="M3" t="s">
-        <v>55</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>56</v>
       </c>
-      <c r="O3" t="s">
-        <v>57</v>
-      </c>
       <c r="P3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q3" t="n">
         <v>0.00194008</v>
@@ -651,19 +633,19 @@
         <v>4.40048E-49</v>
       </c>
       <c r="T3" t="s">
+        <v>63</v>
+      </c>
+      <c r="U3" t="s">
         <v>64</v>
       </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>65</v>
       </c>
-      <c r="V3" t="s">
-        <v>66</v>
-      </c>
       <c r="W3" t="s">
+        <v>66</v>
+      </c>
+      <c r="X3" t="s">
         <v>67</v>
-      </c>
-      <c r="X3" t="s">
-        <v>68</v>
       </c>
       <c r="Y3" t="e">
         <v>#N/A</v>
@@ -699,39 +681,36 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="AJ3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AK3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="AM3" t="n">
         <v>2.0</v>
       </c>
-      <c r="AN3" t="s">
-        <v>67</v>
+      <c r="AM3" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
@@ -746,22 +725,22 @@
         <v>0.614724</v>
       </c>
       <c r="K4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L4" t="s">
+        <v>54</v>
+      </c>
+      <c r="M4" t="s">
+        <v>54</v>
+      </c>
+      <c r="N4" t="s">
         <v>55</v>
       </c>
-      <c r="L4" t="s">
-        <v>55</v>
-      </c>
-      <c r="M4" t="s">
-        <v>55</v>
-      </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>56</v>
       </c>
-      <c r="O4" t="s">
-        <v>57</v>
-      </c>
       <c r="P4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q4" t="n">
         <v>0.00191171</v>
@@ -773,19 +752,19 @@
         <v>3.90032E-70</v>
       </c>
       <c r="T4" t="s">
+        <v>63</v>
+      </c>
+      <c r="U4" t="s">
         <v>64</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>65</v>
       </c>
-      <c r="V4" t="s">
-        <v>66</v>
-      </c>
       <c r="W4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X4" t="s">
         <v>67</v>
-      </c>
-      <c r="X4" t="s">
-        <v>68</v>
       </c>
       <c r="Y4" t="e">
         <v>#N/A</v>
@@ -821,39 +800,36 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="AJ4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AK4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="AM4" t="n">
         <v>2.0</v>
       </c>
-      <c r="AN4" t="s">
-        <v>67</v>
+      <c r="AM4" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
@@ -868,22 +844,22 @@
         <v>0.081972</v>
       </c>
       <c r="K5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L5" t="s">
+        <v>54</v>
+      </c>
+      <c r="M5" t="s">
+        <v>54</v>
+      </c>
+      <c r="N5" t="s">
         <v>55</v>
       </c>
-      <c r="L5" t="s">
-        <v>55</v>
-      </c>
-      <c r="M5" t="s">
-        <v>55</v>
-      </c>
-      <c r="N5" t="s">
+      <c r="O5" t="s">
         <v>56</v>
       </c>
-      <c r="O5" t="s">
-        <v>57</v>
-      </c>
       <c r="P5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q5" t="n">
         <v>0.00345075</v>
@@ -895,19 +871,19 @@
         <v>1.0E-85</v>
       </c>
       <c r="T5" t="s">
+        <v>63</v>
+      </c>
+      <c r="U5" t="s">
         <v>64</v>
       </c>
-      <c r="U5" t="s">
+      <c r="V5" t="s">
         <v>65</v>
       </c>
-      <c r="V5" t="s">
-        <v>66</v>
-      </c>
       <c r="W5" t="s">
+        <v>66</v>
+      </c>
+      <c r="X5" t="s">
         <v>67</v>
-      </c>
-      <c r="X5" t="s">
-        <v>68</v>
       </c>
       <c r="Y5" t="e">
         <v>#N/A</v>
@@ -943,39 +919,36 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="AJ5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AK5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="AM5" t="n">
         <v>2.0</v>
       </c>
-      <c r="AN5" t="s">
-        <v>67</v>
+      <c r="AM5" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
@@ -990,22 +963,22 @@
         <v>0.3193</v>
       </c>
       <c r="K6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L6" t="s">
+        <v>54</v>
+      </c>
+      <c r="M6" t="s">
+        <v>54</v>
+      </c>
+      <c r="N6" t="s">
         <v>55</v>
       </c>
-      <c r="L6" t="s">
-        <v>55</v>
-      </c>
-      <c r="M6" t="s">
-        <v>55</v>
-      </c>
-      <c r="N6" t="s">
+      <c r="O6" t="s">
         <v>56</v>
       </c>
-      <c r="O6" t="s">
-        <v>57</v>
-      </c>
       <c r="P6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q6" t="n">
         <v>0.00200799</v>
@@ -1017,19 +990,19 @@
         <v>7.10068E-73</v>
       </c>
       <c r="T6" t="s">
+        <v>63</v>
+      </c>
+      <c r="U6" t="s">
         <v>64</v>
       </c>
-      <c r="U6" t="s">
+      <c r="V6" t="s">
         <v>65</v>
       </c>
-      <c r="V6" t="s">
-        <v>66</v>
-      </c>
       <c r="W6" t="s">
+        <v>66</v>
+      </c>
+      <c r="X6" t="s">
         <v>67</v>
-      </c>
-      <c r="X6" t="s">
-        <v>68</v>
       </c>
       <c r="Y6" t="e">
         <v>#N/A</v>
@@ -1065,39 +1038,36 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="AJ6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AK6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="AM6" t="n">
         <v>2.0</v>
       </c>
-      <c r="AN6" t="s">
-        <v>67</v>
+      <c r="AM6" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" t="s">
         <v>50</v>
       </c>
-      <c r="C7" t="s">
-        <v>51</v>
-      </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
@@ -1112,22 +1082,22 @@
         <v>0.08288</v>
       </c>
       <c r="K7" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" t="s">
+        <v>54</v>
+      </c>
+      <c r="N7" t="s">
         <v>55</v>
       </c>
-      <c r="L7" t="s">
-        <v>55</v>
-      </c>
-      <c r="M7" t="s">
-        <v>55</v>
-      </c>
-      <c r="N7" t="s">
+      <c r="O7" t="s">
         <v>56</v>
       </c>
-      <c r="O7" t="s">
-        <v>57</v>
-      </c>
       <c r="P7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q7" t="n">
         <v>0.00336822</v>
@@ -1139,19 +1109,19 @@
         <v>4.40048E-88</v>
       </c>
       <c r="T7" t="s">
+        <v>63</v>
+      </c>
+      <c r="U7" t="s">
         <v>64</v>
       </c>
-      <c r="U7" t="s">
+      <c r="V7" t="s">
         <v>65</v>
       </c>
-      <c r="V7" t="s">
-        <v>66</v>
-      </c>
       <c r="W7" t="s">
+        <v>66</v>
+      </c>
+      <c r="X7" t="s">
         <v>67</v>
-      </c>
-      <c r="X7" t="s">
-        <v>68</v>
       </c>
       <c r="Y7" t="e">
         <v>#N/A</v>
@@ -1187,19 +1157,16 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="AJ7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AK7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="AM7" t="n">
         <v>2.0</v>
       </c>
-      <c r="AN7" t="s">
-        <v>67</v>
+      <c r="AM7" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1257,10 +1224,10 @@
         <v>17</v>
       </c>
       <c r="P1" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q1" t="s">
         <v>71</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>72</v>
       </c>
       <c r="R1" t="s">
         <v>15</v>
@@ -1287,36 +1254,33 @@
         <v>35</v>
       </c>
       <c r="Z1" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="AA1" t="s">
         <v>37</v>
       </c>
       <c r="AB1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AC1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
@@ -1331,16 +1295,16 @@
         <v>0.5608</v>
       </c>
       <c r="K2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O2" t="n">
         <v>1.164E-4</v>
@@ -1355,7 +1319,7 @@
         <v>0.0151</v>
       </c>
       <c r="S2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="T2" t="n">
         <v>1.0</v>
@@ -1370,42 +1334,39 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="X2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Y2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.1773814E7</v>
-      </c>
-      <c r="AA2" t="n">
         <v>2.0</v>
       </c>
-      <c r="AB2" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC2" t="e">
+      <c r="AA2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
@@ -1420,16 +1381,16 @@
         <v>0.3735</v>
       </c>
       <c r="K3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O3" t="n">
         <v>6.709E-4</v>
@@ -1444,7 +1405,7 @@
         <v>0.0153</v>
       </c>
       <c r="S3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="T3" t="n">
         <v>2.0</v>
@@ -1459,42 +1420,39 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="X3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Y3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="AA3" t="n">
         <v>2.0</v>
       </c>
-      <c r="AB3" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC3" t="e">
+      <c r="AA3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
@@ -1509,16 +1467,16 @@
         <v>0.5828</v>
       </c>
       <c r="K4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O4" t="n">
         <v>2.354E-6</v>
@@ -1533,7 +1491,7 @@
         <v>0.015</v>
       </c>
       <c r="S4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="T4" t="n">
         <v>3.0</v>
@@ -1548,42 +1506,39 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="X4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Y4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="AA4" t="n">
         <v>2.0</v>
       </c>
-      <c r="AB4" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC4" t="e">
+      <c r="AA4" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
@@ -1598,16 +1553,16 @@
         <v>0.0865</v>
       </c>
       <c r="K5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O5" t="n">
         <v>2.586E-6</v>
@@ -1622,7 +1577,7 @@
         <v>0.0307</v>
       </c>
       <c r="S5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="T5" t="n">
         <v>4.0</v>
@@ -1637,42 +1592,39 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="X5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Y5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="AA5" t="n">
         <v>2.0</v>
       </c>
-      <c r="AB5" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC5" t="e">
+      <c r="AA5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
@@ -1687,16 +1639,16 @@
         <v>0.3404</v>
       </c>
       <c r="K6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O6" t="n">
         <v>3.78E-6</v>
@@ -1711,7 +1663,7 @@
         <v>0.0156</v>
       </c>
       <c r="S6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="T6" t="n">
         <v>5.0</v>
@@ -1726,42 +1678,39 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="X6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Y6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="AA6" t="n">
         <v>2.0</v>
       </c>
-      <c r="AB6" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC6" t="e">
+      <c r="AA6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" t="s">
         <v>50</v>
       </c>
-      <c r="C7" t="s">
-        <v>51</v>
-      </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
@@ -1776,16 +1725,16 @@
         <v>0.098</v>
       </c>
       <c r="K7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O7" t="n">
         <v>2.023E-7</v>
@@ -1800,7 +1749,7 @@
         <v>0.0253</v>
       </c>
       <c r="S7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="T7" t="n">
         <v>6.0</v>
@@ -1815,21 +1764,18 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="X7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Y7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="AA7" t="n">
         <v>2.0</v>
       </c>
-      <c r="AB7" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC7" t="e">
+      <c r="AA7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1938,28 +1884,25 @@
       <c r="AF1" t="s">
         <v>37</v>
       </c>
-      <c r="AG1" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
@@ -1974,22 +1917,22 @@
         <v>0.5563</v>
       </c>
       <c r="K2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="O2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q2" t="n">
         <v>0.0059</v>
@@ -2001,19 +1944,19 @@
         <v>0.2177</v>
       </c>
       <c r="T2" t="s">
+        <v>75</v>
+      </c>
+      <c r="U2" t="s">
+        <v>76</v>
+      </c>
+      <c r="V2" t="s">
         <v>77</v>
       </c>
-      <c r="U2" t="s">
-        <v>78</v>
-      </c>
-      <c r="V2" t="s">
-        <v>79</v>
-      </c>
       <c r="W2" t="s">
+        <v>66</v>
+      </c>
+      <c r="X2" t="s">
         <v>67</v>
-      </c>
-      <c r="X2" t="s">
-        <v>68</v>
       </c>
       <c r="Y2" t="n">
         <v>1.0</v>
@@ -2028,39 +1971,36 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="AC2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AD2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AE2" t="n">
-        <v>4.1773814E7</v>
-      </c>
-      <c r="AF2" t="n">
         <v>2.0</v>
       </c>
-      <c r="AG2" t="s">
-        <v>67</v>
+      <c r="AF2" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
@@ -2075,22 +2015,22 @@
         <v>0.368</v>
       </c>
       <c r="K3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="O3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q3" t="n">
         <v>0.0059</v>
@@ -2102,19 +2042,19 @@
         <v>0.1696</v>
       </c>
       <c r="T3" t="s">
+        <v>75</v>
+      </c>
+      <c r="U3" t="s">
+        <v>76</v>
+      </c>
+      <c r="V3" t="s">
         <v>77</v>
       </c>
-      <c r="U3" t="s">
-        <v>78</v>
-      </c>
-      <c r="V3" t="s">
-        <v>79</v>
-      </c>
       <c r="W3" t="s">
+        <v>66</v>
+      </c>
+      <c r="X3" t="s">
         <v>67</v>
-      </c>
-      <c r="X3" t="s">
-        <v>68</v>
       </c>
       <c r="Y3" t="n">
         <v>2.0</v>
@@ -2129,39 +2069,36 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="AC3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AD3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AE3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="AF3" t="n">
         <v>2.0</v>
       </c>
-      <c r="AG3" t="s">
-        <v>67</v>
+      <c r="AF3" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
@@ -2176,22 +2113,22 @@
         <v>0.5991</v>
       </c>
       <c r="K4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="O4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q4" t="n">
         <v>0.0058</v>
@@ -2203,19 +2140,19 @@
         <v>0.0456604</v>
       </c>
       <c r="T4" t="s">
+        <v>75</v>
+      </c>
+      <c r="U4" t="s">
+        <v>76</v>
+      </c>
+      <c r="V4" t="s">
         <v>77</v>
       </c>
-      <c r="U4" t="s">
-        <v>78</v>
-      </c>
-      <c r="V4" t="s">
-        <v>79</v>
-      </c>
       <c r="W4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X4" t="s">
         <v>67</v>
-      </c>
-      <c r="X4" t="s">
-        <v>68</v>
       </c>
       <c r="Y4" t="n">
         <v>3.0</v>
@@ -2230,39 +2167,36 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="AC4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AD4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AE4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="AF4" t="n">
         <v>2.0</v>
       </c>
-      <c r="AG4" t="s">
-        <v>67</v>
+      <c r="AF4" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
@@ -2277,22 +2211,22 @@
         <v>0.0795</v>
       </c>
       <c r="K5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="O5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q5" t="n">
         <v>0.0111</v>
@@ -2304,19 +2238,19 @@
         <v>0.2391</v>
       </c>
       <c r="T5" t="s">
+        <v>75</v>
+      </c>
+      <c r="U5" t="s">
+        <v>76</v>
+      </c>
+      <c r="V5" t="s">
         <v>77</v>
       </c>
-      <c r="U5" t="s">
-        <v>78</v>
-      </c>
-      <c r="V5" t="s">
-        <v>79</v>
-      </c>
       <c r="W5" t="s">
+        <v>66</v>
+      </c>
+      <c r="X5" t="s">
         <v>67</v>
-      </c>
-      <c r="X5" t="s">
-        <v>68</v>
       </c>
       <c r="Y5" t="n">
         <v>4.0</v>
@@ -2331,39 +2265,36 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="AC5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AD5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AE5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="AF5" t="n">
         <v>2.0</v>
       </c>
-      <c r="AG5" t="s">
-        <v>67</v>
+      <c r="AF5" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
@@ -2378,22 +2309,22 @@
         <v>0.307</v>
       </c>
       <c r="K6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="O6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q6" t="n">
         <v>0.0062</v>
@@ -2405,19 +2336,19 @@
         <v>0.0199802</v>
       </c>
       <c r="T6" t="s">
+        <v>75</v>
+      </c>
+      <c r="U6" t="s">
+        <v>76</v>
+      </c>
+      <c r="V6" t="s">
         <v>77</v>
       </c>
-      <c r="U6" t="s">
-        <v>78</v>
-      </c>
-      <c r="V6" t="s">
-        <v>79</v>
-      </c>
       <c r="W6" t="s">
+        <v>66</v>
+      </c>
+      <c r="X6" t="s">
         <v>67</v>
-      </c>
-      <c r="X6" t="s">
-        <v>68</v>
       </c>
       <c r="Y6" t="n">
         <v>5.0</v>
@@ -2432,39 +2363,36 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="AC6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AD6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AE6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="AF6" t="n">
         <v>2.0</v>
       </c>
-      <c r="AG6" t="s">
-        <v>67</v>
+      <c r="AF6" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" t="s">
         <v>50</v>
       </c>
-      <c r="C7" t="s">
-        <v>51</v>
-      </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
@@ -2479,22 +2407,22 @@
         <v>0.0747</v>
       </c>
       <c r="K7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="O7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q7" t="n">
         <v>0.0111</v>
@@ -2506,19 +2434,19 @@
         <v>0.2969</v>
       </c>
       <c r="T7" t="s">
+        <v>75</v>
+      </c>
+      <c r="U7" t="s">
+        <v>76</v>
+      </c>
+      <c r="V7" t="s">
         <v>77</v>
       </c>
-      <c r="U7" t="s">
-        <v>78</v>
-      </c>
-      <c r="V7" t="s">
-        <v>79</v>
-      </c>
       <c r="W7" t="s">
+        <v>66</v>
+      </c>
+      <c r="X7" t="s">
         <v>67</v>
-      </c>
-      <c r="X7" t="s">
-        <v>68</v>
       </c>
       <c r="Y7" t="n">
         <v>6.0</v>
@@ -2533,19 +2461,16 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="AC7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AD7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AE7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="AF7" t="n">
         <v>2.0</v>
       </c>
-      <c r="AG7" t="s">
-        <v>67</v>
+      <c r="AF7" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -2653,28 +2578,25 @@
       <c r="AF1" t="s">
         <v>37</v>
       </c>
-      <c r="AG1" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
@@ -2689,22 +2611,22 @@
         <v>0.561269</v>
       </c>
       <c r="K2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q2" t="n">
         <v>0.007812</v>
@@ -2716,19 +2638,19 @@
         <v>0.127364</v>
       </c>
       <c r="T2" t="s">
+        <v>79</v>
+      </c>
+      <c r="U2" t="s">
+        <v>80</v>
+      </c>
+      <c r="V2" t="s">
         <v>81</v>
       </c>
-      <c r="U2" t="s">
-        <v>82</v>
-      </c>
-      <c r="V2" t="s">
-        <v>83</v>
-      </c>
       <c r="W2" t="s">
+        <v>66</v>
+      </c>
+      <c r="X2" t="s">
         <v>67</v>
-      </c>
-      <c r="X2" t="s">
-        <v>68</v>
       </c>
       <c r="Y2" t="n">
         <v>1.0</v>
@@ -2743,39 +2665,36 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="AC2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AD2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AE2" t="n">
-        <v>4.1773814E7</v>
-      </c>
-      <c r="AF2" t="n">
         <v>2.0</v>
       </c>
-      <c r="AG2" t="s">
-        <v>67</v>
+      <c r="AF2" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
@@ -2790,22 +2709,22 @@
         <v>0.362718</v>
       </c>
       <c r="K3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q3" t="n">
         <v>0.007769</v>
@@ -2817,19 +2736,19 @@
         <v>0.204175</v>
       </c>
       <c r="T3" t="s">
+        <v>79</v>
+      </c>
+      <c r="U3" t="s">
+        <v>80</v>
+      </c>
+      <c r="V3" t="s">
         <v>81</v>
       </c>
-      <c r="U3" t="s">
-        <v>82</v>
-      </c>
-      <c r="V3" t="s">
-        <v>83</v>
-      </c>
       <c r="W3" t="s">
+        <v>66</v>
+      </c>
+      <c r="X3" t="s">
         <v>67</v>
-      </c>
-      <c r="X3" t="s">
-        <v>68</v>
       </c>
       <c r="Y3" t="n">
         <v>2.0</v>
@@ -2844,39 +2763,36 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="AC3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AD3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AE3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="AF3" t="n">
         <v>2.0</v>
       </c>
-      <c r="AG3" t="s">
-        <v>67</v>
+      <c r="AF3" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
@@ -2891,22 +2807,22 @@
         <v>0.6033580000000001</v>
       </c>
       <c r="K4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q4" t="n">
         <v>0.007615</v>
@@ -2918,19 +2834,19 @@
         <v>0.173892</v>
       </c>
       <c r="T4" t="s">
+        <v>79</v>
+      </c>
+      <c r="U4" t="s">
+        <v>80</v>
+      </c>
+      <c r="V4" t="s">
         <v>81</v>
       </c>
-      <c r="U4" t="s">
-        <v>82</v>
-      </c>
-      <c r="V4" t="s">
-        <v>83</v>
-      </c>
       <c r="W4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X4" t="s">
         <v>67</v>
-      </c>
-      <c r="X4" t="s">
-        <v>68</v>
       </c>
       <c r="Y4" t="n">
         <v>3.0</v>
@@ -2945,39 +2861,36 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="AC4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AD4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AE4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="AF4" t="n">
         <v>2.0</v>
       </c>
-      <c r="AG4" t="s">
-        <v>67</v>
+      <c r="AF4" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
@@ -2992,22 +2905,22 @@
         <v>0.076448</v>
       </c>
       <c r="K5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q5" t="n">
         <v>0.015085</v>
@@ -3019,19 +2932,19 @@
         <v>0.0670054</v>
       </c>
       <c r="T5" t="s">
+        <v>79</v>
+      </c>
+      <c r="U5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" t="s">
         <v>81</v>
       </c>
-      <c r="U5" t="s">
-        <v>82</v>
-      </c>
-      <c r="V5" t="s">
-        <v>83</v>
-      </c>
       <c r="W5" t="s">
+        <v>66</v>
+      </c>
+      <c r="X5" t="s">
         <v>67</v>
-      </c>
-      <c r="X5" t="s">
-        <v>68</v>
       </c>
       <c r="Y5" t="n">
         <v>4.0</v>
@@ -3046,39 +2959,36 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="AC5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AD5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AE5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="AF5" t="n">
         <v>2.0</v>
       </c>
-      <c r="AG5" t="s">
-        <v>67</v>
+      <c r="AF5" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
@@ -3093,22 +3003,22 @@
         <v>0.29944</v>
       </c>
       <c r="K6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q6" t="n">
         <v>0.008282</v>
@@ -3120,19 +3030,19 @@
         <v>0.130477</v>
       </c>
       <c r="T6" t="s">
+        <v>79</v>
+      </c>
+      <c r="U6" t="s">
+        <v>80</v>
+      </c>
+      <c r="V6" t="s">
         <v>81</v>
       </c>
-      <c r="U6" t="s">
-        <v>82</v>
-      </c>
-      <c r="V6" t="s">
-        <v>83</v>
-      </c>
       <c r="W6" t="s">
+        <v>66</v>
+      </c>
+      <c r="X6" t="s">
         <v>67</v>
-      </c>
-      <c r="X6" t="s">
-        <v>68</v>
       </c>
       <c r="Y6" t="n">
         <v>5.0</v>
@@ -3147,39 +3057,36 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="AC6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AD6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AE6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="AF6" t="n">
         <v>2.0</v>
       </c>
-      <c r="AG6" t="s">
-        <v>67</v>
+      <c r="AF6" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" t="s">
         <v>50</v>
       </c>
-      <c r="C7" t="s">
-        <v>51</v>
-      </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
@@ -3194,22 +3101,22 @@
         <v>0.071269</v>
       </c>
       <c r="K7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q7" t="n">
         <v>0.014973</v>
@@ -3221,19 +3128,19 @@
         <v>0.0379962</v>
       </c>
       <c r="T7" t="s">
+        <v>79</v>
+      </c>
+      <c r="U7" t="s">
+        <v>80</v>
+      </c>
+      <c r="V7" t="s">
         <v>81</v>
       </c>
-      <c r="U7" t="s">
-        <v>82</v>
-      </c>
-      <c r="V7" t="s">
-        <v>83</v>
-      </c>
       <c r="W7" t="s">
+        <v>66</v>
+      </c>
+      <c r="X7" t="s">
         <v>67</v>
-      </c>
-      <c r="X7" t="s">
-        <v>68</v>
       </c>
       <c r="Y7" t="n">
         <v>6.0</v>
@@ -3248,19 +3155,16 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="AC7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AD7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AE7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="AF7" t="n">
         <v>2.0</v>
       </c>
-      <c r="AG7" t="s">
-        <v>67</v>
+      <c r="AF7" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -3342,69 +3246,66 @@
         <v>35</v>
       </c>
       <c r="X1" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="Y1" t="s">
         <v>37</v>
       </c>
       <c r="Z1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0114</v>
+        <v>-0.0128</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5939</v>
+        <v>0.5619</v>
       </c>
       <c r="K2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0074</v>
+        <v>0.0075</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1241</v>
+        <v>0.08812</v>
       </c>
       <c r="Q2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="R2" t="n">
         <v>1.0</v>
@@ -3419,42 +3320,39 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="W2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="X2" t="n">
-        <v>4.1773814E7</v>
-      </c>
-      <c r="Y2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Z2" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="Y2" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
@@ -3469,16 +3367,16 @@
         <v>0.3711</v>
       </c>
       <c r="K3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="O3" t="n">
         <v>0.0075</v>
@@ -3487,7 +3385,7 @@
         <v>0.4928</v>
       </c>
       <c r="Q3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="R3" t="n">
         <v>2.0</v>
@@ -3502,42 +3400,39 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="W3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="X3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="Y3" t="n">
         <v>2.0</v>
       </c>
-      <c r="Z3" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA3" t="e">
+      <c r="Y3" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
@@ -3552,16 +3447,16 @@
         <v>0.5896</v>
       </c>
       <c r="K4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="O4" t="n">
         <v>0.0071</v>
@@ -3570,7 +3465,7 @@
         <v>0.1022</v>
       </c>
       <c r="Q4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="R4" t="n">
         <v>3.0</v>
@@ -3585,42 +3480,39 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="W4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="X4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y4" t="n">
         <v>2.0</v>
       </c>
-      <c r="Z4" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA4" t="e">
+      <c r="Y4" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
@@ -3635,16 +3527,16 @@
         <v>0.0844</v>
       </c>
       <c r="K5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="O5" t="n">
         <v>0.0144</v>
@@ -3653,7 +3545,7 @@
         <v>0.778</v>
       </c>
       <c r="Q5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="R5" t="n">
         <v>4.0</v>
@@ -3668,42 +3560,39 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="W5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="X5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="Y5" t="n">
         <v>2.0</v>
       </c>
-      <c r="Z5" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA5" t="e">
+      <c r="Y5" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
@@ -3718,16 +3607,16 @@
         <v>0.3322</v>
       </c>
       <c r="K6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="O6" t="n">
         <v>0.0074</v>
@@ -3736,7 +3625,7 @@
         <v>0.6207</v>
       </c>
       <c r="Q6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="R6" t="n">
         <v>5.0</v>
@@ -3751,42 +3640,39 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="W6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="X6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="Y6" t="n">
         <v>2.0</v>
       </c>
-      <c r="Z6" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA6" t="e">
+      <c r="Y6" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" t="s">
         <v>50</v>
       </c>
-      <c r="C7" t="s">
-        <v>51</v>
-      </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
@@ -3801,16 +3687,16 @@
         <v>0.0935</v>
       </c>
       <c r="K7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="O7" t="n">
         <v>0.0125</v>
@@ -3819,7 +3705,7 @@
         <v>0.6618</v>
       </c>
       <c r="Q7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="R7" t="n">
         <v>6.0</v>
@@ -3834,21 +3720,18 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="W7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="X7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="Y7" t="n">
         <v>2.0</v>
       </c>
-      <c r="Z7" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA7" t="e">
+      <c r="Y7" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3957,28 +3840,25 @@
       <c r="AF1" t="s">
         <v>37</v>
       </c>
-      <c r="AG1" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
@@ -3993,22 +3873,22 @@
         <v>0.575037</v>
       </c>
       <c r="K2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q2" t="n">
         <v>9.31355E-4</v>
@@ -4020,19 +3900,19 @@
         <v>0.7</v>
       </c>
       <c r="T2" t="s">
+        <v>84</v>
+      </c>
+      <c r="U2" t="s">
+        <v>85</v>
+      </c>
+      <c r="V2" t="s">
         <v>86</v>
       </c>
-      <c r="U2" t="s">
-        <v>87</v>
-      </c>
-      <c r="V2" t="s">
-        <v>88</v>
-      </c>
       <c r="W2" t="s">
+        <v>66</v>
+      </c>
+      <c r="X2" t="s">
         <v>67</v>
-      </c>
-      <c r="X2" t="s">
-        <v>68</v>
       </c>
       <c r="Y2" t="n">
         <v>1.0</v>
@@ -4047,39 +3927,36 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="AC2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AD2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AE2" t="n">
-        <v>4.1773814E7</v>
-      </c>
-      <c r="AF2" t="n">
         <v>2.0</v>
       </c>
-      <c r="AG2" t="s">
-        <v>67</v>
+      <c r="AF2" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
@@ -4094,22 +3971,22 @@
         <v>0.360018</v>
       </c>
       <c r="K3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q3" t="n">
         <v>9.41774E-4</v>
@@ -4121,19 +3998,19 @@
         <v>0.58</v>
       </c>
       <c r="T3" t="s">
+        <v>84</v>
+      </c>
+      <c r="U3" t="s">
+        <v>85</v>
+      </c>
+      <c r="V3" t="s">
         <v>86</v>
       </c>
-      <c r="U3" t="s">
-        <v>87</v>
-      </c>
-      <c r="V3" t="s">
-        <v>88</v>
-      </c>
       <c r="W3" t="s">
+        <v>66</v>
+      </c>
+      <c r="X3" t="s">
         <v>67</v>
-      </c>
-      <c r="X3" t="s">
-        <v>68</v>
       </c>
       <c r="Y3" t="n">
         <v>2.0</v>
@@ -4148,39 +4025,36 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="AC3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AD3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AE3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="AF3" t="n">
         <v>2.0</v>
       </c>
-      <c r="AG3" t="s">
-        <v>67</v>
+      <c r="AF3" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
@@ -4195,22 +4069,22 @@
         <v>0.613402</v>
       </c>
       <c r="K4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q4" t="n">
         <v>9.27905E-4</v>
@@ -4222,19 +4096,19 @@
         <v>0.54</v>
       </c>
       <c r="T4" t="s">
+        <v>84</v>
+      </c>
+      <c r="U4" t="s">
+        <v>85</v>
+      </c>
+      <c r="V4" t="s">
         <v>86</v>
       </c>
-      <c r="U4" t="s">
-        <v>87</v>
-      </c>
-      <c r="V4" t="s">
-        <v>88</v>
-      </c>
       <c r="W4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X4" t="s">
         <v>67</v>
-      </c>
-      <c r="X4" t="s">
-        <v>68</v>
       </c>
       <c r="Y4" t="n">
         <v>3.0</v>
@@ -4249,39 +4123,36 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="AC4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AD4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AE4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="AF4" t="n">
         <v>2.0</v>
       </c>
-      <c r="AG4" t="s">
-        <v>67</v>
+      <c r="AF4" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
@@ -4296,22 +4167,22 @@
         <v>0.08108</v>
       </c>
       <c r="K5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q5" t="n">
         <v>0.0016853</v>
@@ -4323,19 +4194,19 @@
         <v>0.0749998</v>
       </c>
       <c r="T5" t="s">
+        <v>84</v>
+      </c>
+      <c r="U5" t="s">
+        <v>85</v>
+      </c>
+      <c r="V5" t="s">
         <v>86</v>
       </c>
-      <c r="U5" t="s">
-        <v>87</v>
-      </c>
-      <c r="V5" t="s">
-        <v>88</v>
-      </c>
       <c r="W5" t="s">
+        <v>66</v>
+      </c>
+      <c r="X5" t="s">
         <v>67</v>
-      </c>
-      <c r="X5" t="s">
-        <v>68</v>
       </c>
       <c r="Y5" t="n">
         <v>4.0</v>
@@ -4350,39 +4221,36 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="AC5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AD5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AE5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="AF5" t="n">
         <v>2.0</v>
       </c>
-      <c r="AG5" t="s">
-        <v>67</v>
+      <c r="AF5" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
@@ -4397,22 +4265,22 @@
         <v>0.320025</v>
       </c>
       <c r="K6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q6" t="n">
         <v>9.74984E-4</v>
@@ -4424,19 +4292,19 @@
         <v>0.2</v>
       </c>
       <c r="T6" t="s">
+        <v>84</v>
+      </c>
+      <c r="U6" t="s">
+        <v>85</v>
+      </c>
+      <c r="V6" t="s">
         <v>86</v>
       </c>
-      <c r="U6" t="s">
-        <v>87</v>
-      </c>
-      <c r="V6" t="s">
-        <v>88</v>
-      </c>
       <c r="W6" t="s">
+        <v>66</v>
+      </c>
+      <c r="X6" t="s">
         <v>67</v>
-      </c>
-      <c r="X6" t="s">
-        <v>68</v>
       </c>
       <c r="Y6" t="n">
         <v>5.0</v>
@@ -4451,39 +4319,36 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="AC6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AD6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AE6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="AF6" t="n">
         <v>2.0</v>
       </c>
-      <c r="AG6" t="s">
-        <v>67</v>
+      <c r="AF6" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" t="s">
         <v>50</v>
       </c>
-      <c r="C7" t="s">
-        <v>51</v>
-      </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
@@ -4498,22 +4363,22 @@
         <v>0.081717</v>
       </c>
       <c r="K7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q7" t="n">
         <v>0.00164674</v>
@@ -4525,19 +4390,19 @@
         <v>0.34</v>
       </c>
       <c r="T7" t="s">
+        <v>84</v>
+      </c>
+      <c r="U7" t="s">
+        <v>85</v>
+      </c>
+      <c r="V7" t="s">
         <v>86</v>
       </c>
-      <c r="U7" t="s">
-        <v>87</v>
-      </c>
-      <c r="V7" t="s">
-        <v>88</v>
-      </c>
       <c r="W7" t="s">
+        <v>66</v>
+      </c>
+      <c r="X7" t="s">
         <v>67</v>
-      </c>
-      <c r="X7" t="s">
-        <v>68</v>
       </c>
       <c r="Y7" t="n">
         <v>6.0</v>
@@ -4552,19 +4417,16 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="AC7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AD7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AE7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="AF7" t="n">
         <v>2.0</v>
       </c>
-      <c r="AG7" t="s">
-        <v>67</v>
+      <c r="AF7" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -4693,28 +4555,25 @@
       <c r="AM1" t="s">
         <v>37</v>
       </c>
-      <c r="AN1" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
@@ -4729,22 +4588,22 @@
         <v>0.608197</v>
       </c>
       <c r="K2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="O2" t="s">
+        <v>56</v>
+      </c>
+      <c r="P2" t="s">
         <v>57</v>
-      </c>
-      <c r="P2" t="s">
-        <v>90</v>
       </c>
       <c r="Q2" t="n">
         <v>0.0081</v>
@@ -4756,40 +4615,40 @@
         <v>0.2432</v>
       </c>
       <c r="T2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="U2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="V2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="W2" t="s">
+        <v>66</v>
+      </c>
+      <c r="X2" t="s">
         <v>67</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA2" t="s">
         <v>68</v>
       </c>
-      <c r="Y2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>94</v>
-      </c>
       <c r="AB2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AC2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AE2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AF2" t="n">
         <v>1.0</v>
@@ -4804,39 +4663,36 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="AJ2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AK2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.1773814E7</v>
-      </c>
-      <c r="AM2" t="n">
         <v>2.0</v>
       </c>
-      <c r="AN2" t="s">
-        <v>67</v>
+      <c r="AM2" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
@@ -4851,22 +4707,22 @@
         <v>0.358299</v>
       </c>
       <c r="K3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="O3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q3" t="n">
         <v>0.0082</v>
@@ -4878,19 +4734,19 @@
         <v>0.23</v>
       </c>
       <c r="T3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="U3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="V3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="W3" t="s">
+        <v>66</v>
+      </c>
+      <c r="X3" t="s">
         <v>67</v>
-      </c>
-      <c r="X3" t="s">
-        <v>68</v>
       </c>
       <c r="Y3" t="e">
         <v>#N/A</v>
@@ -4926,39 +4782,36 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="AJ3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AK3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="AM3" t="n">
         <v>2.0</v>
       </c>
-      <c r="AN3" t="s">
-        <v>67</v>
+      <c r="AM3" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
@@ -4973,22 +4826,22 @@
         <v>0.6135740000000001</v>
       </c>
       <c r="K4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="O4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q4" t="n">
         <v>0.008</v>
@@ -5000,19 +4853,19 @@
         <v>0.1725</v>
       </c>
       <c r="T4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="U4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="V4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="W4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X4" t="s">
         <v>67</v>
-      </c>
-      <c r="X4" t="s">
-        <v>68</v>
       </c>
       <c r="Y4" t="e">
         <v>#N/A</v>
@@ -5048,39 +4901,36 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="AJ4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AK4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="AM4" t="n">
         <v>2.0</v>
       </c>
-      <c r="AN4" t="s">
-        <v>67</v>
+      <c r="AM4" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G5" t="n">
         <v>0.036955</v>
@@ -5095,22 +4945,22 @@
         <v>0.315314</v>
       </c>
       <c r="K5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="O5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q5" t="n">
         <v>0.0085</v>
@@ -5122,19 +4972,19 @@
         <v>0.1318</v>
       </c>
       <c r="T5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="U5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="V5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="W5" t="s">
+        <v>66</v>
+      </c>
+      <c r="X5" t="s">
         <v>67</v>
-      </c>
-      <c r="X5" t="s">
-        <v>68</v>
       </c>
       <c r="Y5" t="e">
         <v>#N/A</v>
@@ -5170,39 +5020,36 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="AJ5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AK5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="AM5" t="n">
         <v>2.0</v>
       </c>
-      <c r="AN5" t="s">
-        <v>67</v>
+      <c r="AM5" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" t="s">
         <v>50</v>
       </c>
-      <c r="C6" t="s">
-        <v>51</v>
-      </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G6" t="n">
         <v>0.060792</v>
@@ -5217,22 +5064,22 @@
         <v>0.0801682</v>
       </c>
       <c r="K6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="O6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q6" t="n">
         <v>0.0146</v>
@@ -5244,19 +5091,19 @@
         <v>0.9881</v>
       </c>
       <c r="T6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="U6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="V6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="W6" t="s">
+        <v>66</v>
+      </c>
+      <c r="X6" t="s">
         <v>67</v>
-      </c>
-      <c r="X6" t="s">
-        <v>68</v>
       </c>
       <c r="Y6" t="e">
         <v>#N/A</v>
@@ -5292,19 +5139,16 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="AJ6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AK6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="AM6" t="n">
         <v>2.0</v>
       </c>
-      <c r="AN6" t="s">
-        <v>67</v>
+      <c r="AM6" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
